--- a/Result/profitability/3684.xlsx
+++ b/Result/profitability/3684.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM65"/>
+  <dimension ref="A1:AM66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.65</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7862500000000001</v>
+        <v>0.87875</v>
       </c>
       <c r="N2" t="n">
-        <v>32.65375</v>
+        <v>32.8525</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.74</v>
       </c>
       <c r="M3" t="n">
-        <v>0.835</v>
+        <v>0.83375</v>
       </c>
       <c r="N3" t="n">
-        <v>33.35125</v>
+        <v>33.3325</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.48</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7575000000000001</v>
+        <v>0.825</v>
       </c>
       <c r="N4" t="n">
-        <v>32.965</v>
+        <v>32.96</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.25</v>
       </c>
       <c r="M5" t="n">
-        <v>0.72</v>
+        <v>0.7725</v>
       </c>
       <c r="N5" t="n">
-        <v>32.3975</v>
+        <v>32.75125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.5</v>
       </c>
       <c r="M6" t="n">
-        <v>0.69875</v>
+        <v>0.6699999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>33.0775</v>
+        <v>33.15</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -8687,6 +8687,133 @@
       </c>
       <c r="AM65" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>3684</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>329</v>
+      </c>
+      <c r="D66" t="n">
+        <v>220</v>
+      </c>
+      <c r="E66" t="n">
+        <v>109</v>
+      </c>
+      <c r="F66" t="n">
+        <v>33.18</v>
+      </c>
+      <c r="G66" t="n">
+        <v>43</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>13.10%</t>
+        </is>
+      </c>
+      <c r="I66" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J66" t="n">
+        <v>39</v>
+      </c>
+      <c r="K66" t="n">
+        <v>33</v>
+      </c>
+      <c r="L66" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0.8412500000000001</v>
+      </c>
+      <c r="N66" t="n">
+        <v>32.93375</v>
+      </c>
+      <c r="O66" t="n">
+        <v>1</v>
+      </c>
+      <c r="P66" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>0</v>
+      </c>
+      <c r="R66" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" t="n">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>0</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
+      </c>
+      <c r="V66" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W66" t="n">
+        <v>0.3900000000000001</v>
+      </c>
+      <c r="X66" t="n">
+        <v>0.5571428571428574</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>-1.93</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>-0.05497009399031616</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>0.6268656716417911</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>2.829999999999998</v>
+      </c>
+      <c r="AD66" t="n">
+        <v>0.09324546952224044</v>
+      </c>
+      <c r="AE66" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF66" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH66" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI66" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK66" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL66" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM66" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
